--- a/cadet_data/CadetData_OCP.xlsx
+++ b/cadet_data/CadetData_OCP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94a1dad5ec87e9ff/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94a1dad5ec87e9ff/Documents/Programming/A4Uniforms/cadet_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5CAFBD3-1D62-491F-BD94-851ABB7F90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{A5CAFBD3-1D62-491F-BD94-851ABB7F90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{744B9C75-1311-4F94-BBF0-2E24D34FC33A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{907332DD-76B0-480E-A8E0-9F05B6AFB941}"/>
   </bookViews>
@@ -47,81 +47,6 @@
     <t>Gender</t>
   </si>
   <si>
-    <t>Blouse Size</t>
-  </si>
-  <si>
-    <t>Blouse Qty</t>
-  </si>
-  <si>
-    <t>Hot Weather Blouse Size</t>
-  </si>
-  <si>
-    <t>Hot Weather Blouse Qty</t>
-  </si>
-  <si>
-    <t>Pant Size</t>
-  </si>
-  <si>
-    <t>Pant Qty</t>
-  </si>
-  <si>
-    <t>Hot Weather Pant Size</t>
-  </si>
-  <si>
-    <t>Hot Weather Pant Qty</t>
-  </si>
-  <si>
-    <t>Fleece Size</t>
-  </si>
-  <si>
-    <t>Fleece Qty</t>
-  </si>
-  <si>
-    <t>Sand Tee Size</t>
-  </si>
-  <si>
-    <t>Sand Tee Qty</t>
-  </si>
-  <si>
-    <t>Boot Size</t>
-  </si>
-  <si>
-    <t>Boot Qty</t>
-  </si>
-  <si>
-    <t>Patrol Cap Size</t>
-  </si>
-  <si>
-    <t>Patrol Cap Qty</t>
-  </si>
-  <si>
-    <t>Watch Cap Size</t>
-  </si>
-  <si>
-    <t>Watch Cap Qty</t>
-  </si>
-  <si>
-    <t>OCP Belt Size</t>
-  </si>
-  <si>
-    <t>OCP Belt Qty</t>
-  </si>
-  <si>
-    <t>Flight Suit Size</t>
-  </si>
-  <si>
-    <t>Flight Suit Qty</t>
-  </si>
-  <si>
-    <t>Flight Jacket Size</t>
-  </si>
-  <si>
-    <t>Flight Jacket Qty</t>
-  </si>
-  <si>
-    <t>Allen, Michael</t>
-  </si>
-  <si>
     <t>AS100</t>
   </si>
   <si>
@@ -143,9 +68,6 @@
     <t>S/M</t>
   </si>
   <si>
-    <t>Calderon, Mia</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -161,9 +83,6 @@
     <t>7R</t>
   </si>
   <si>
-    <t>Emmons, Mckenzie</t>
-  </si>
-  <si>
     <t>M/S</t>
   </si>
   <si>
@@ -173,36 +92,21 @@
     <t>8W</t>
   </si>
   <si>
-    <t>Guttman, Ryan</t>
-  </si>
-  <si>
     <t>S/L</t>
   </si>
   <si>
     <t>12R</t>
   </si>
   <si>
-    <t>Kieselowsky, Sofiya</t>
-  </si>
-  <si>
     <t>XS/S</t>
   </si>
   <si>
-    <t>Krenk, Spencer</t>
-  </si>
-  <si>
     <t>AS150</t>
   </si>
   <si>
-    <t>Roy, Ritika</t>
-  </si>
-  <si>
     <t>9.5R</t>
   </si>
   <si>
-    <t>Spurlock, Liam</t>
-  </si>
-  <si>
     <t>3XL/L</t>
   </si>
   <si>
@@ -215,12 +119,6 @@
     <t>L/XL</t>
   </si>
   <si>
-    <t>Tsoi, Thomas</t>
-  </si>
-  <si>
-    <t>Anand, Hrishikesh</t>
-  </si>
-  <si>
     <t>AS200</t>
   </si>
   <si>
@@ -230,30 +128,18 @@
     <t>One-size</t>
   </si>
   <si>
-    <t>Ben-Zvi, Ari</t>
-  </si>
-  <si>
     <t>9R</t>
   </si>
   <si>
-    <t>Besana, Anastasia</t>
-  </si>
-  <si>
     <t>XS/XS</t>
   </si>
   <si>
     <t>5R?</t>
   </si>
   <si>
-    <t>Chung, Ethan</t>
-  </si>
-  <si>
     <t>8.5N</t>
   </si>
   <si>
-    <t>Elnasser, Zaid</t>
-  </si>
-  <si>
     <t>XL/L</t>
   </si>
   <si>
@@ -266,216 +152,78 @@
     <t>13R</t>
   </si>
   <si>
-    <t>Gentile, Nicholas</t>
-  </si>
-  <si>
     <t>11R</t>
   </si>
   <si>
-    <t>Gerst, Tyler</t>
-  </si>
-  <si>
     <t>AS250</t>
   </si>
   <si>
     <t>10R</t>
   </si>
   <si>
-    <t>Gopalakrishnan, Laya</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
     <t>8.5R</t>
   </si>
   <si>
-    <t>Harold, Danille</t>
-  </si>
-  <si>
     <t>AS500</t>
   </si>
   <si>
     <t>6N</t>
   </si>
   <si>
-    <t>Kelly, Connor</t>
-  </si>
-  <si>
-    <t>Maria, Antonio</t>
-  </si>
-  <si>
     <t>M/XL</t>
   </si>
   <si>
     <t>L/L</t>
   </si>
   <si>
-    <t>McCarthy, Norah</t>
-  </si>
-  <si>
-    <t>Miller, Kenneth</t>
-  </si>
-  <si>
     <t>12.5R</t>
   </si>
   <si>
-    <t>Nacanaynay, Jakob</t>
-  </si>
-  <si>
-    <t>Park, Jekemiah</t>
-  </si>
-  <si>
     <t>L/S</t>
   </si>
   <si>
-    <t>Racette, Nicholas</t>
-  </si>
-  <si>
-    <t>Smiley, Samuel</t>
-  </si>
-  <si>
     <t>10W</t>
   </si>
   <si>
-    <t>Sokolowski, James</t>
-  </si>
-  <si>
     <t>12W</t>
   </si>
   <si>
-    <t>Tama, Charlotte</t>
-  </si>
-  <si>
     <t>7.5R</t>
   </si>
   <si>
-    <t>Yap, Nicholas</t>
-  </si>
-  <si>
-    <t>Chaney, Jack</t>
-  </si>
-  <si>
     <t>AS300</t>
   </si>
   <si>
-    <t>Chung, Hanna</t>
-  </si>
-  <si>
     <t>XS</t>
   </si>
   <si>
     <t>6.5R</t>
   </si>
   <si>
-    <t>Fujimoto, Andrew</t>
-  </si>
-  <si>
-    <t>Marino, Frank</t>
-  </si>
-  <si>
-    <t>Martini, Marco</t>
-  </si>
-  <si>
-    <t>Martins, Anket</t>
-  </si>
-  <si>
-    <t>McBride, Lindsey</t>
-  </si>
-  <si>
-    <t>Melton, Dawson</t>
-  </si>
-  <si>
     <t>11.5R</t>
   </si>
   <si>
-    <t>Rahman, Nadia</t>
-  </si>
-  <si>
-    <t>7.5W, 8W</t>
-  </si>
-  <si>
-    <t>1, 1</t>
-  </si>
-  <si>
-    <t>Randall, Conrad</t>
-  </si>
-  <si>
-    <t>Shegogue, Thomas</t>
-  </si>
-  <si>
-    <t>Stallone, Thomas</t>
-  </si>
-  <si>
-    <t>Viani, Jared</t>
-  </si>
-  <si>
-    <t>Zegunia, Julia</t>
-  </si>
-  <si>
     <t>8R</t>
   </si>
   <si>
-    <t>Annor, Reginald</t>
-  </si>
-  <si>
     <t>AS400</t>
   </si>
   <si>
     <t>13W</t>
   </si>
   <si>
-    <t>Chilukuri, Sathya</t>
-  </si>
-  <si>
     <t>103.5R</t>
   </si>
   <si>
-    <t>Ettinger, Sophie</t>
-  </si>
-  <si>
-    <t>Fancher, Phillip</t>
-  </si>
-  <si>
-    <t>Hunt, Elyse</t>
-  </si>
-  <si>
-    <t>S/S, S/R</t>
-  </si>
-  <si>
-    <t>34, 40</t>
-  </si>
-  <si>
-    <t>Isaac, Charles</t>
-  </si>
-  <si>
-    <t>Kim, Leo</t>
-  </si>
-  <si>
     <t>40R</t>
   </si>
   <si>
-    <t>Long, John</t>
-  </si>
-  <si>
     <t>44R</t>
   </si>
   <si>
-    <t>Perez, Rodrigo</t>
-  </si>
-  <si>
-    <t>Scalfani-Cohen, Andrew</t>
-  </si>
-  <si>
-    <t>Szymanski, Zoe</t>
-  </si>
-  <si>
-    <t>Teague, Katie</t>
-  </si>
-  <si>
-    <t>Tremel, Pulani</t>
-  </si>
-  <si>
     <t>5R</t>
   </si>
   <si>
@@ -483,6 +231,258 @@
   </si>
   <si>
     <t>Missing</t>
+  </si>
+  <si>
+    <t>BlouseSize</t>
+  </si>
+  <si>
+    <t>BlouseQty</t>
+  </si>
+  <si>
+    <t>HotWeatherBlouseSize</t>
+  </si>
+  <si>
+    <t>HotWeatherBlouseQty</t>
+  </si>
+  <si>
+    <t>PantSize</t>
+  </si>
+  <si>
+    <t>PantQty</t>
+  </si>
+  <si>
+    <t>HotWeatherPantSize</t>
+  </si>
+  <si>
+    <t>HotWeatherPantQty</t>
+  </si>
+  <si>
+    <t>FleeceSize</t>
+  </si>
+  <si>
+    <t>FleeceQty</t>
+  </si>
+  <si>
+    <t>SandTeeSize</t>
+  </si>
+  <si>
+    <t>SandTeeQty</t>
+  </si>
+  <si>
+    <t>BootSize</t>
+  </si>
+  <si>
+    <t>BootQty</t>
+  </si>
+  <si>
+    <t>PatrolCapSize</t>
+  </si>
+  <si>
+    <t>PatrolCapQty</t>
+  </si>
+  <si>
+    <t>WatchCapSize</t>
+  </si>
+  <si>
+    <t>WatchCapQty</t>
+  </si>
+  <si>
+    <t>OCPBeltSize</t>
+  </si>
+  <si>
+    <t>OCPBeltQty</t>
+  </si>
+  <si>
+    <t>FlightSuitSize</t>
+  </si>
+  <si>
+    <t>FlightSuitQty</t>
+  </si>
+  <si>
+    <t>FlightJacketSize</t>
+  </si>
+  <si>
+    <t>FlightJacketQty</t>
+  </si>
+  <si>
+    <t>Allen,Michael</t>
+  </si>
+  <si>
+    <t>Calderon,Mia</t>
+  </si>
+  <si>
+    <t>Emmons,Mckenzie</t>
+  </si>
+  <si>
+    <t>Guttman,Ryan</t>
+  </si>
+  <si>
+    <t>Kieselowsky,Sofiya</t>
+  </si>
+  <si>
+    <t>Krenk,Spencer</t>
+  </si>
+  <si>
+    <t>Roy,Ritika</t>
+  </si>
+  <si>
+    <t>Spurlock,Liam</t>
+  </si>
+  <si>
+    <t>Tsoi,Thomas</t>
+  </si>
+  <si>
+    <t>Anand,Hrishikesh</t>
+  </si>
+  <si>
+    <t>Ben-Zvi,Ari</t>
+  </si>
+  <si>
+    <t>Besana,Anastasia</t>
+  </si>
+  <si>
+    <t>Chung,Ethan</t>
+  </si>
+  <si>
+    <t>Elnasser,Zaid</t>
+  </si>
+  <si>
+    <t>Gentile,Nicholas</t>
+  </si>
+  <si>
+    <t>Gerst,Tyler</t>
+  </si>
+  <si>
+    <t>Gopalakrishnan,Laya</t>
+  </si>
+  <si>
+    <t>Harold,Danille</t>
+  </si>
+  <si>
+    <t>Kelly,Connor</t>
+  </si>
+  <si>
+    <t>Maria,Antonio</t>
+  </si>
+  <si>
+    <t>McCarthy,Norah</t>
+  </si>
+  <si>
+    <t>Miller,Kenneth</t>
+  </si>
+  <si>
+    <t>Nacanaynay,Jakob</t>
+  </si>
+  <si>
+    <t>Park,Jekemiah</t>
+  </si>
+  <si>
+    <t>Racette,Nicholas</t>
+  </si>
+  <si>
+    <t>Smiley,Samuel</t>
+  </si>
+  <si>
+    <t>Sokolowski,James</t>
+  </si>
+  <si>
+    <t>Tama,Charlotte</t>
+  </si>
+  <si>
+    <t>Yap,Nicholas</t>
+  </si>
+  <si>
+    <t>Chaney,Jack</t>
+  </si>
+  <si>
+    <t>Chung,Hanna</t>
+  </si>
+  <si>
+    <t>Fujimoto,Andrew</t>
+  </si>
+  <si>
+    <t>Marino,Frank</t>
+  </si>
+  <si>
+    <t>Martini,Marco</t>
+  </si>
+  <si>
+    <t>Martins,Anket</t>
+  </si>
+  <si>
+    <t>McBride,Lindsey</t>
+  </si>
+  <si>
+    <t>Melton,Dawson</t>
+  </si>
+  <si>
+    <t>Rahman,Nadia</t>
+  </si>
+  <si>
+    <t>7.5W,8W</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>Randall,Conrad</t>
+  </si>
+  <si>
+    <t>Shegogue,Thomas</t>
+  </si>
+  <si>
+    <t>Stallone,Thomas</t>
+  </si>
+  <si>
+    <t>Viani,Jared</t>
+  </si>
+  <si>
+    <t>Zegunia,Julia</t>
+  </si>
+  <si>
+    <t>Annor,Reginald</t>
+  </si>
+  <si>
+    <t>Chilukuri,Sathya</t>
+  </si>
+  <si>
+    <t>Ettinger,Sophie</t>
+  </si>
+  <si>
+    <t>Fancher,Phillip</t>
+  </si>
+  <si>
+    <t>Hunt,Elyse</t>
+  </si>
+  <si>
+    <t>S/S,S/R</t>
+  </si>
+  <si>
+    <t>34,40</t>
+  </si>
+  <si>
+    <t>Isaac,Charles</t>
+  </si>
+  <si>
+    <t>Kim,Leo</t>
+  </si>
+  <si>
+    <t>Long,John</t>
+  </si>
+  <si>
+    <t>Perez,Rodrigo</t>
+  </si>
+  <si>
+    <t>Scalfani-Cohen,Andrew</t>
+  </si>
+  <si>
+    <t>Szymanski,Zoe</t>
+  </si>
+  <si>
+    <t>Teague,Katie</t>
+  </si>
+  <si>
+    <t>Tremel,Pulani</t>
   </si>
 </sst>
 </file>
@@ -1288,126 +1288,126 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E2" s="12">
         <v>1</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G2" s="13">
         <v>0</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I2" s="12">
         <v>1</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K2" s="16">
         <v>0</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M2" s="12">
         <v>1</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O2" s="12">
         <v>1</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Q2" s="12">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="T2" s="11" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="U2" s="12">
         <v>1</v>
@@ -1431,13 +1431,13 @@
         <v>1</v>
       </c>
       <c r="X2" s="15" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y2" s="12">
         <v>0</v>
       </c>
       <c r="Z2" s="15" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA2" s="12">
         <v>0</v>
@@ -1445,52 +1445,52 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E3" s="21">
         <v>1</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G3" s="22">
         <v>0</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I3" s="21">
         <v>1</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K3" s="22">
         <v>0</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="M3" s="21">
         <v>1</v>
       </c>
       <c r="N3" s="20" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O3" s="21">
         <v>1</v>
       </c>
       <c r="P3" s="20" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="Q3" s="21">
         <v>1</v>
@@ -1502,7 +1502,7 @@
         <v>1</v>
       </c>
       <c r="T3" s="20" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="U3" s="21">
         <v>1</v>
@@ -1514,13 +1514,13 @@
         <v>1</v>
       </c>
       <c r="X3" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y3" s="21">
         <v>0</v>
       </c>
       <c r="Z3" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA3" s="21">
         <v>0</v>
@@ -1528,52 +1528,52 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E4" s="12">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G4" s="13">
         <v>0</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I4" s="12">
         <v>1</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K4" s="13">
         <v>0</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M4" s="12">
         <v>1</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O4" s="12">
         <v>1</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="12">
         <v>1</v>
@@ -1585,7 +1585,7 @@
         <v>1</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="U4" s="12">
         <v>1</v>
@@ -1597,13 +1597,13 @@
         <v>1</v>
       </c>
       <c r="X4" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y4" s="12">
         <v>0</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA4" s="12">
         <v>0</v>
@@ -1611,52 +1611,52 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E5" s="21">
         <v>1</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G5" s="22">
         <v>0</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="I5" s="21">
         <v>1</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K5" s="22">
         <v>0</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="M5" s="21">
         <v>1</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O5" s="21">
         <v>1</v>
       </c>
       <c r="P5" s="20" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="Q5" s="21">
         <v>1</v>
@@ -1668,7 +1668,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="20" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="U5" s="21">
         <v>1</v>
@@ -1680,13 +1680,13 @@
         <v>1</v>
       </c>
       <c r="X5" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="21">
         <v>0</v>
       </c>
       <c r="Z5" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="21">
         <v>0</v>
@@ -1694,52 +1694,52 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E6" s="12">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G6" s="13">
         <v>0</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I6" s="12">
         <v>1</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K6" s="13">
         <v>0</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="M6" s="12">
         <v>1</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O6" s="12">
         <v>1</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="Q6" s="12">
         <v>1</v>
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="U6" s="12">
         <v>1</v>
@@ -1763,13 +1763,13 @@
         <v>1</v>
       </c>
       <c r="X6" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y6" s="12">
         <v>0</v>
       </c>
       <c r="Z6" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA6" s="12">
         <v>0</v>
@@ -1777,13 +1777,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="27"/>
@@ -1818,52 +1818,52 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G8" s="13">
         <v>0</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I8" s="12">
         <v>1</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K8" s="13">
         <v>0</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="M8" s="12">
         <v>1</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O8" s="12">
         <v>1</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="Q8" s="12">
         <v>1</v>
@@ -1875,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="11" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="U8" s="12">
         <v>1</v>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y8" s="12">
         <v>0</v>
       </c>
       <c r="Z8" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA8" s="12">
         <v>0</v>
@@ -1901,50 +1901,50 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="E9" s="21">
         <v>1</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G9" s="22">
         <v>0</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="I9" s="21">
         <v>1</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K9" s="22">
         <v>0</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="M9" s="21"/>
       <c r="N9" s="20" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="O9" s="21">
         <v>1</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="Q9" s="21">
         <v>1</v>
@@ -1956,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="20" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="U9" s="21">
         <v>1</v>
@@ -1968,13 +1968,13 @@
         <v>1</v>
       </c>
       <c r="X9" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y9" s="21">
         <v>0</v>
       </c>
       <c r="Z9" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="21">
         <v>0</v>
@@ -1982,52 +1982,52 @@
     </row>
     <row r="10" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E10" s="36">
         <v>1</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G10" s="37">
         <v>0</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I10" s="36">
         <v>1</v>
       </c>
       <c r="J10" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K10" s="37">
         <v>0</v>
       </c>
       <c r="L10" s="38" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M10" s="36">
         <v>1</v>
       </c>
       <c r="N10" s="35" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O10" s="36">
         <v>1</v>
       </c>
       <c r="P10" s="35" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Q10" s="36">
         <v>1</v>
@@ -2039,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="T10" s="35" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="U10" s="36">
         <v>1</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="X10" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="36">
         <v>0</v>
       </c>
       <c r="Z10" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="36">
         <v>0</v>
@@ -2065,52 +2065,52 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="40" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E11" s="44">
         <v>1</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G11" s="45">
         <v>0</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="I11" s="44">
         <v>1</v>
       </c>
       <c r="J11" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K11" s="45">
         <v>0</v>
       </c>
       <c r="L11" s="46" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="M11" s="44">
         <v>1</v>
       </c>
       <c r="N11" s="43" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O11" s="44">
         <v>1</v>
       </c>
       <c r="P11" s="43" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="Q11" s="44">
         <v>1</v>
@@ -2122,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="43" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U11" s="44">
         <v>1</v>
@@ -2134,13 +2134,13 @@
         <v>1</v>
       </c>
       <c r="X11" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="44">
         <v>0</v>
       </c>
       <c r="Z11" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA11" s="44">
         <v>0</v>
@@ -2148,52 +2148,52 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G12" s="13">
         <v>0</v>
       </c>
       <c r="H12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="12">
+        <v>1</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="12">
+        <v>1</v>
+      </c>
+      <c r="P12" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="I12" s="12">
-        <v>1</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="12">
-        <v>1</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" s="12">
-        <v>1</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>65</v>
       </c>
       <c r="Q12" s="12">
         <v>1</v>
@@ -2205,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U12" s="12">
         <v>1</v>
@@ -2217,13 +2217,13 @@
         <v>1</v>
       </c>
       <c r="X12" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="12">
         <v>0</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="12">
         <v>0</v>
@@ -2231,52 +2231,52 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E13" s="21">
         <v>1</v>
       </c>
       <c r="F13" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="22">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="22">
-        <v>0</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>67</v>
-      </c>
       <c r="I13" s="21">
         <v>1</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K13" s="22">
         <v>0</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="M13" s="21">
         <v>1</v>
       </c>
       <c r="N13" s="20" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O13" s="21">
         <v>1</v>
       </c>
       <c r="P13" s="20" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="21">
         <v>1</v>
@@ -2288,25 +2288,25 @@
         <v>1</v>
       </c>
       <c r="T13" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U13" s="21">
         <v>1</v>
       </c>
       <c r="V13" s="20" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="W13" s="21">
         <v>1</v>
       </c>
       <c r="X13" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y13" s="21">
         <v>0</v>
       </c>
       <c r="Z13" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="21">
         <v>0</v>
@@ -2314,52 +2314,52 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E14" s="12">
         <v>1</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I14" s="12">
         <v>1</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K14" s="13">
         <v>0</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="M14" s="12">
         <v>1</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O14" s="12">
         <v>1</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="Q14" s="12">
         <v>1</v>
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="T14" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U14" s="12">
         <v>1</v>
@@ -2383,13 +2383,13 @@
         <v>1</v>
       </c>
       <c r="X14" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="12">
         <v>0</v>
       </c>
       <c r="Z14" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA14" s="12">
         <v>0</v>
@@ -2397,52 +2397,52 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E15" s="21">
         <v>1</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G15" s="22">
         <v>0</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="I15" s="21">
         <v>1</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K15" s="22">
         <v>0</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="M15" s="21">
         <v>1</v>
       </c>
       <c r="N15" s="20" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="O15" s="21">
         <v>1</v>
       </c>
       <c r="P15" s="20" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="Q15" s="21">
         <v>1</v>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U15" s="21">
         <v>1</v>
@@ -2466,13 +2466,13 @@
         <v>1</v>
       </c>
       <c r="X15" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y15" s="21">
         <v>0</v>
       </c>
       <c r="Z15" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA15" s="21">
         <v>0</v>
@@ -2480,52 +2480,52 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E16" s="12">
         <v>1</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I16" s="12">
         <v>1</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
       </c>
       <c r="L16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="12">
+        <v>1</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O16" s="12">
+        <v>1</v>
+      </c>
+      <c r="P16" s="11" t="s">
         <v>38</v>
-      </c>
-      <c r="M16" s="12">
-        <v>1</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="O16" s="12">
-        <v>1</v>
-      </c>
-      <c r="P16" s="11" t="s">
-        <v>77</v>
       </c>
       <c r="Q16" s="12">
         <v>1</v>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U16" s="12">
         <v>1</v>
@@ -2549,13 +2549,13 @@
         <v>1</v>
       </c>
       <c r="X16" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y16" s="12">
         <v>0</v>
       </c>
       <c r="Z16" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA16" s="12">
         <v>0</v>
@@ -2563,52 +2563,52 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E17" s="21">
         <v>1</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G17" s="22">
         <v>0</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I17" s="21">
         <v>1</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K17" s="22">
         <v>0</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M17" s="21">
         <v>1</v>
       </c>
       <c r="N17" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O17" s="21">
         <v>1</v>
       </c>
       <c r="P17" s="20" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q17" s="21">
         <v>1</v>
@@ -2620,7 +2620,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U17" s="21">
         <v>1</v>
@@ -2632,13 +2632,13 @@
         <v>1</v>
       </c>
       <c r="X17" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y17" s="21">
         <v>0</v>
       </c>
       <c r="Z17" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA17" s="21">
         <v>0</v>
@@ -2646,52 +2646,52 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E18" s="12">
         <v>1</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I18" s="12">
         <v>1</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="M18" s="12">
         <v>1</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O18" s="12">
         <v>1</v>
       </c>
       <c r="P18" s="11" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="Q18" s="12">
         <v>1</v>
@@ -2703,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U18" s="12">
         <v>1</v>
@@ -2715,13 +2715,13 @@
         <v>1</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y18" s="12">
         <v>0</v>
       </c>
       <c r="Z18" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA18" s="12">
         <v>0</v>
@@ -2729,52 +2729,52 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E19" s="21">
         <v>1</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G19" s="22">
         <v>0</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I19" s="21">
         <v>1</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K19" s="22">
         <v>0</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M19" s="21">
         <v>1</v>
       </c>
       <c r="N19" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O19" s="21">
         <v>1</v>
       </c>
       <c r="P19" s="20" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="Q19" s="21">
         <v>1</v>
@@ -2786,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="T19" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U19" s="21">
         <v>1</v>
@@ -2798,13 +2798,13 @@
         <v>1</v>
       </c>
       <c r="X19" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y19" s="21">
         <v>0</v>
       </c>
       <c r="Z19" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA19" s="21">
         <v>0</v>
@@ -2812,52 +2812,52 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E20" s="12">
         <v>1</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G20" s="13">
         <v>0</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I20" s="12">
         <v>1</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M20" s="12">
         <v>1</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O20" s="12">
         <v>1</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Q20" s="12">
         <v>1</v>
@@ -2869,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U20" s="12">
         <v>1</v>
@@ -2881,13 +2881,13 @@
         <v>1</v>
       </c>
       <c r="X20" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y20" s="12">
         <v>0</v>
       </c>
       <c r="Z20" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA20" s="12">
         <v>0</v>
@@ -2895,52 +2895,52 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="E21" s="21">
         <v>1</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G21" s="22">
         <v>0</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="I21" s="21">
         <v>1</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K21" s="22">
         <v>0</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="M21" s="21">
         <v>1</v>
       </c>
       <c r="N21" s="20" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O21" s="21">
         <v>1</v>
       </c>
       <c r="P21" s="20" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="Q21" s="21">
         <v>1</v>
@@ -2952,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="T21" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U21" s="21">
         <v>1</v>
@@ -2964,13 +2964,13 @@
         <v>1</v>
       </c>
       <c r="X21" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y21" s="21">
         <v>0</v>
       </c>
       <c r="Z21" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA21" s="21">
         <v>0</v>
@@ -2978,52 +2978,52 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E22" s="12">
         <v>1</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G22" s="13">
         <v>0</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I22" s="12">
         <v>1</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K22" s="13">
         <v>0</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M22" s="12">
         <v>1</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O22" s="12">
         <v>1</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Q22" s="12">
         <v>1</v>
@@ -3035,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U22" s="12">
         <v>1</v>
@@ -3047,13 +3047,13 @@
         <v>1</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y22" s="12">
         <v>0</v>
       </c>
       <c r="Z22" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA22" s="12">
         <v>0</v>
@@ -3061,52 +3061,52 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E23" s="21">
         <v>1</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G23" s="22">
         <v>0</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="I23" s="21">
         <v>1</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K23" s="22">
         <v>0</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="M23" s="21">
         <v>1</v>
       </c>
       <c r="N23" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O23" s="21">
         <v>1</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="Q23" s="21">
         <v>1</v>
@@ -3118,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="T23" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U23" s="21">
         <v>1</v>
@@ -3130,13 +3130,13 @@
         <v>1</v>
       </c>
       <c r="X23" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y23" s="21">
         <v>0</v>
       </c>
       <c r="Z23" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA23" s="21">
         <v>0</v>
@@ -3144,52 +3144,52 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E24" s="12">
         <v>1</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G24" s="13">
         <v>0</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I24" s="12">
         <v>1</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K24" s="13">
         <v>0</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M24" s="12">
         <v>1</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O24" s="12">
         <v>1</v>
       </c>
       <c r="P24" s="11" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="Q24" s="12">
         <v>1</v>
@@ -3201,25 +3201,25 @@
         <v>1</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U24" s="12">
         <v>1</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="W24" s="12">
         <v>1</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y24" s="12">
         <v>0</v>
       </c>
       <c r="Z24" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA24" s="12">
         <v>0</v>
@@ -3227,64 +3227,64 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C25" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="21">
+        <v>1</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="22">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="21">
+        <v>1</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="22">
+        <v>0</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="21">
+        <v>1</v>
+      </c>
+      <c r="N25" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="O25" s="21">
+        <v>1</v>
+      </c>
+      <c r="P25" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q25" s="21">
+        <v>1</v>
+      </c>
+      <c r="R25" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="S25" s="21">
+        <v>1</v>
+      </c>
+      <c r="T25" s="20" t="s">
         <v>29</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="21">
-        <v>1</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="22">
-        <v>0</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25" s="21">
-        <v>1</v>
-      </c>
-      <c r="J25" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="K25" s="22">
-        <v>0</v>
-      </c>
-      <c r="L25" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="M25" s="21">
-        <v>1</v>
-      </c>
-      <c r="N25" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O25" s="21">
-        <v>1</v>
-      </c>
-      <c r="P25" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q25" s="21">
-        <v>1</v>
-      </c>
-      <c r="R25" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="S25" s="21">
-        <v>1</v>
-      </c>
-      <c r="T25" s="20" t="s">
-        <v>63</v>
       </c>
       <c r="U25" s="21">
         <v>1</v>
@@ -3296,13 +3296,13 @@
         <v>1</v>
       </c>
       <c r="X25" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y25" s="21">
         <v>0</v>
       </c>
       <c r="Z25" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA25" s="21">
         <v>0</v>
@@ -3310,52 +3310,52 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E26" s="12">
         <v>1</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G26" s="13">
         <v>0</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I26" s="12">
         <v>1</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K26" s="13">
         <v>0</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M26" s="12">
         <v>1</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O26" s="12">
         <v>1</v>
       </c>
       <c r="P26" s="11" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="Q26" s="12">
         <v>1</v>
@@ -3367,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U26" s="12">
         <v>1</v>
@@ -3379,13 +3379,13 @@
         <v>1</v>
       </c>
       <c r="X26" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y26" s="12">
         <v>0</v>
       </c>
       <c r="Z26" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA26" s="12">
         <v>0</v>
@@ -3393,52 +3393,52 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E27" s="21">
         <v>1</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G27" s="22">
         <v>0</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I27" s="21">
         <v>1</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K27" s="22">
         <v>0</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M27" s="21">
         <v>1</v>
       </c>
       <c r="N27" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O27" s="21">
         <v>1</v>
       </c>
       <c r="P27" s="20" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="Q27" s="21">
         <v>1</v>
@@ -3450,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U27" s="21">
         <v>1</v>
@@ -3462,13 +3462,13 @@
         <v>1</v>
       </c>
       <c r="X27" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y27" s="21">
         <v>0</v>
       </c>
       <c r="Z27" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA27" s="21">
         <v>0</v>
@@ -3476,52 +3476,52 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E28" s="12">
         <v>1</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G28" s="13">
         <v>0</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I28" s="12">
         <v>1</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K28" s="13">
         <v>0</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="M28" s="12">
         <v>1</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O28" s="12">
         <v>1</v>
       </c>
       <c r="P28" s="11" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="Q28" s="12">
         <v>1</v>
@@ -3533,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U28" s="12">
         <v>1</v>
@@ -3545,13 +3545,13 @@
         <v>1</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y28" s="12">
         <v>0</v>
       </c>
       <c r="Z28" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA28" s="12">
         <v>0</v>
@@ -3559,52 +3559,52 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E29" s="21">
         <v>1</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G29" s="22">
         <v>0</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="I29" s="21">
         <v>1</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K29" s="22">
         <v>0</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M29" s="21">
         <v>1</v>
       </c>
       <c r="N29" s="20" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O29" s="21">
         <v>1</v>
       </c>
       <c r="P29" s="20" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="Q29" s="21">
         <v>1</v>
@@ -3616,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U29" s="21">
         <v>1</v>
@@ -3628,13 +3628,13 @@
         <v>1</v>
       </c>
       <c r="X29" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y29" s="21">
         <v>0</v>
       </c>
       <c r="Z29" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA29" s="21">
         <v>0</v>
@@ -3642,52 +3642,52 @@
     </row>
     <row r="30" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="48" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E30" s="36">
         <v>1</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G30" s="37">
         <v>0</v>
       </c>
       <c r="H30" s="38" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I30" s="36">
         <v>1</v>
       </c>
       <c r="J30" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K30" s="37">
         <v>0</v>
       </c>
       <c r="L30" s="38" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M30" s="36">
         <v>1</v>
       </c>
       <c r="N30" s="35" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O30" s="36">
         <v>1</v>
       </c>
       <c r="P30" s="35" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="36">
         <v>1</v>
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="T30" s="35" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U30" s="36">
         <v>1</v>
@@ -3711,13 +3711,13 @@
         <v>1</v>
       </c>
       <c r="X30" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y30" s="36">
         <v>0</v>
       </c>
       <c r="Z30" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA30" s="36">
         <v>0</v>
@@ -3725,52 +3725,52 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="40" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E31" s="44">
         <v>2</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G31" s="45">
         <v>0</v>
       </c>
       <c r="H31" s="46" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I31" s="44">
         <v>2</v>
       </c>
       <c r="J31" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K31" s="45">
         <v>0</v>
       </c>
       <c r="L31" s="46" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M31" s="44">
         <v>1</v>
       </c>
       <c r="N31" s="43" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O31" s="44">
         <v>5</v>
       </c>
       <c r="P31" s="43" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="Q31" s="44">
         <v>1</v>
@@ -3782,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="T31" s="43" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U31" s="44">
         <v>1</v>
@@ -3794,13 +3794,13 @@
         <v>1</v>
       </c>
       <c r="X31" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y31" s="44">
         <v>0</v>
       </c>
       <c r="Z31" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA31" s="44">
         <v>0</v>
@@ -3808,52 +3808,52 @@
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E32" s="12">
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G32" s="13">
         <v>0</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I32" s="12">
         <v>1</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K32" s="13">
         <v>0</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="M32" s="12">
         <v>1</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="O32" s="12">
         <v>1</v>
       </c>
       <c r="P32" s="11" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="Q32" s="12">
         <v>1</v>
@@ -3865,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U32" s="12">
         <v>1</v>
@@ -3877,13 +3877,13 @@
         <v>1</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y32" s="12">
         <v>0</v>
       </c>
       <c r="Z32" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA32" s="12">
         <v>0</v>
@@ -3891,52 +3891,52 @@
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E33" s="21">
         <v>1</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G33" s="22">
         <v>0</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I33" s="21">
         <v>1</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K33" s="22">
         <v>0</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M33" s="21">
         <v>1</v>
       </c>
       <c r="N33" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O33" s="21">
         <v>6</v>
       </c>
       <c r="P33" s="20" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="Q33" s="21">
         <v>1</v>
@@ -3948,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="T33" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U33" s="21">
         <v>1</v>
@@ -3960,13 +3960,13 @@
         <v>1</v>
       </c>
       <c r="X33" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y33" s="21">
         <v>0</v>
       </c>
       <c r="Z33" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA33" s="21">
         <v>0</v>
@@ -3974,52 +3974,52 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E34" s="12">
         <v>0</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G34" s="13">
         <v>2</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="I34" s="12">
         <v>0</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K34" s="13">
         <v>3</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M34" s="12">
         <v>1</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O34" s="12">
         <v>6</v>
       </c>
       <c r="P34" s="11" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="Q34" s="12">
         <v>1</v>
@@ -4031,25 +4031,25 @@
         <v>1</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U34" s="12">
         <v>1</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="W34" s="12">
         <v>1</v>
       </c>
       <c r="X34" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y34" s="12">
         <v>0</v>
       </c>
       <c r="Z34" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA34" s="12">
         <v>0</v>
@@ -4057,64 +4057,64 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E35" s="21">
         <v>2</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G35" s="22">
         <v>1</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I35" s="21">
         <v>1</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K35" s="22">
         <v>1</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M35" s="21">
         <v>1</v>
       </c>
       <c r="N35" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O35" s="21">
         <v>5</v>
       </c>
       <c r="P35" s="20" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Q35" s="21">
         <v>1</v>
       </c>
       <c r="R35" s="20" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="S35" s="21">
         <v>1</v>
       </c>
       <c r="T35" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U35" s="21">
         <v>1</v>
@@ -4126,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="X35" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y35" s="21">
         <v>0</v>
       </c>
       <c r="Z35" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA35" s="21">
         <v>0</v>
@@ -4140,52 +4140,52 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="E36" s="12">
         <v>0</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G36" s="13">
         <v>2</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="I36" s="12">
         <v>1</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="K36" s="13">
         <v>2</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="M36" s="12">
         <v>1</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O36" s="12">
         <v>5</v>
       </c>
       <c r="P36" s="11" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="Q36" s="12">
         <v>1</v>
@@ -4197,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U36" s="12">
         <v>1</v>
@@ -4209,13 +4209,13 @@
         <v>1</v>
       </c>
       <c r="X36" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y36" s="12">
         <v>0</v>
       </c>
       <c r="Z36" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA36" s="12">
         <v>0</v>
@@ -4223,52 +4223,52 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="17" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E37" s="21">
         <v>1</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G37" s="22">
         <v>0</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I37" s="21">
         <v>1</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K37" s="22">
         <v>0</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M37" s="21">
         <v>1</v>
       </c>
       <c r="N37" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O37" s="21">
         <v>6</v>
       </c>
       <c r="P37" s="20" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Q37" s="21">
         <v>1</v>
@@ -4280,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="T37" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U37" s="21">
         <v>1</v>
@@ -4292,13 +4292,13 @@
         <v>1</v>
       </c>
       <c r="X37" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y37" s="21">
         <v>0</v>
       </c>
       <c r="Z37" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA37" s="21">
         <v>0</v>
@@ -4306,52 +4306,52 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E38" s="12">
         <v>1</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G38" s="13">
         <v>0</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="I38" s="12">
         <v>1</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K38" s="13">
         <v>0</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M38" s="12">
         <v>1</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O38" s="12">
         <v>6</v>
       </c>
       <c r="P38" s="11" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="Q38" s="12">
         <v>1</v>
@@ -4363,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U38" s="12">
         <v>1</v>
@@ -4375,13 +4375,13 @@
         <v>1</v>
       </c>
       <c r="X38" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y38" s="12">
         <v>0</v>
       </c>
       <c r="Z38" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA38" s="12">
         <v>0</v>
@@ -4389,55 +4389,55 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="17" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E39" s="21">
         <v>2</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G39" s="22">
         <v>0</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I39" s="21">
         <v>1</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K39" s="22">
         <v>0</v>
       </c>
       <c r="L39" s="23" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="M39" s="21">
         <v>1</v>
       </c>
       <c r="N39" s="20" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O39" s="21">
         <v>6</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="Q39" s="21" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="R39" s="24">
         <v>7.125</v>
@@ -4446,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U39" s="21">
         <v>1</v>
@@ -4458,13 +4458,13 @@
         <v>1</v>
       </c>
       <c r="X39" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y39" s="21">
         <v>0</v>
       </c>
       <c r="Z39" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA39" s="21">
         <v>0</v>
@@ -4472,52 +4472,52 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E40" s="12">
         <v>1</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G40" s="13">
         <v>0</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I40" s="12">
         <v>1</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K40" s="13">
         <v>0</v>
       </c>
       <c r="L40" s="14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M40" s="12">
         <v>1</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O40" s="12">
         <v>1</v>
       </c>
       <c r="P40" s="11" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Q40" s="12">
         <v>1</v>
@@ -4529,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U40" s="12">
         <v>1</v>
@@ -4541,13 +4541,13 @@
         <v>1</v>
       </c>
       <c r="X40" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y40" s="12">
         <v>0</v>
       </c>
       <c r="Z40" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA40" s="12">
         <v>0</v>
@@ -4555,52 +4555,52 @@
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E41" s="21">
         <v>1</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G41" s="22">
         <v>0</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I41" s="21">
         <v>1</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K41" s="22">
         <v>0</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M41" s="21">
         <v>1</v>
       </c>
       <c r="N41" s="20" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O41" s="21">
         <v>1</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="Q41" s="21">
         <v>1</v>
@@ -4612,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U41" s="21">
         <v>1</v>
@@ -4624,13 +4624,13 @@
         <v>1</v>
       </c>
       <c r="X41" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y41" s="21">
         <v>0</v>
       </c>
       <c r="Z41" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA41" s="21">
         <v>0</v>
@@ -4638,52 +4638,52 @@
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E42" s="12">
         <v>1</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G42" s="13">
         <v>0</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I42" s="12">
         <v>1</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K42" s="13">
         <v>0</v>
       </c>
       <c r="L42" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="M42" s="12">
         <v>1</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O42" s="12">
         <v>3</v>
       </c>
       <c r="P42" s="11" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="Q42" s="12">
         <v>1</v>
@@ -4695,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U42" s="12">
         <v>1</v>
@@ -4707,13 +4707,13 @@
         <v>1</v>
       </c>
       <c r="X42" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y42" s="12">
         <v>0</v>
       </c>
       <c r="Z42" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA42" s="12">
         <v>0</v>
@@ -4721,52 +4721,52 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E43" s="21">
         <v>1</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G43" s="22">
         <v>0</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I43" s="21">
         <v>1</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K43" s="22">
         <v>0</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M43" s="21">
         <v>1</v>
       </c>
       <c r="N43" s="20" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O43" s="21">
         <v>6</v>
       </c>
       <c r="P43" s="20" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="Q43" s="21">
         <v>1</v>
@@ -4778,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U43" s="21">
         <v>1</v>
@@ -4790,13 +4790,13 @@
         <v>1</v>
       </c>
       <c r="X43" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y43" s="21">
         <v>0</v>
       </c>
       <c r="Z43" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA43" s="21">
         <v>0</v>
@@ -4804,52 +4804,52 @@
     </row>
     <row r="44" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="48" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E44" s="36">
         <v>1</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G44" s="37">
         <v>0</v>
       </c>
       <c r="H44" s="38" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I44" s="36">
         <v>1</v>
       </c>
       <c r="J44" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K44" s="37">
         <v>0</v>
       </c>
       <c r="L44" s="38" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M44" s="36">
         <v>1</v>
       </c>
       <c r="N44" s="35" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O44" s="36">
         <v>4</v>
       </c>
       <c r="P44" s="35" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="Q44" s="36">
         <v>1</v>
@@ -4861,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="T44" s="35" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U44" s="36">
         <v>1</v>
@@ -4873,13 +4873,13 @@
         <v>1</v>
       </c>
       <c r="X44" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y44" s="36">
         <v>0</v>
       </c>
       <c r="Z44" s="35" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA44" s="36">
         <v>0</v>
@@ -4887,52 +4887,52 @@
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="40" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B45" s="41" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E45" s="44">
         <v>4</v>
       </c>
       <c r="F45" s="43" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G45" s="45">
         <v>3</v>
       </c>
       <c r="H45" s="46" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="I45" s="44">
         <v>4</v>
       </c>
       <c r="J45" s="43" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="K45" s="45">
         <v>3</v>
       </c>
       <c r="L45" s="46" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="M45" s="44">
         <v>1</v>
       </c>
       <c r="N45" s="43" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O45" s="44">
         <v>3</v>
       </c>
       <c r="P45" s="43" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="Q45" s="44">
         <v>1</v>
@@ -4944,7 +4944,7 @@
         <v>1</v>
       </c>
       <c r="T45" s="43" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U45" s="44">
         <v>1</v>
@@ -4956,13 +4956,13 @@
         <v>1</v>
       </c>
       <c r="X45" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y45" s="44">
         <v>0</v>
       </c>
       <c r="Z45" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA45" s="44">
         <v>0</v>
@@ -4970,52 +4970,52 @@
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E46" s="12">
         <v>1</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G46" s="13">
         <v>2</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="I46" s="12">
         <v>1</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="K46" s="13">
         <v>2</v>
       </c>
       <c r="L46" s="14" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="M46" s="12">
         <v>1</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O46" s="12">
         <v>1</v>
       </c>
       <c r="P46" s="11" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="Q46" s="12">
         <v>1</v>
@@ -5027,7 +5027,7 @@
         <v>2</v>
       </c>
       <c r="T46" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U46" s="12">
         <v>1</v>
@@ -5039,13 +5039,13 @@
         <v>1</v>
       </c>
       <c r="X46" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y46" s="12">
         <v>0</v>
       </c>
       <c r="Z46" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA46" s="12">
         <v>0</v>
@@ -5053,52 +5053,52 @@
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E47" s="21">
         <v>2</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G47" s="22">
         <v>2</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I47" s="21">
         <v>2</v>
       </c>
       <c r="J47" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K47" s="22">
         <v>2</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M47" s="21">
         <v>1</v>
       </c>
       <c r="N47" s="20" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O47" s="21">
         <v>3</v>
       </c>
       <c r="P47" s="20" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="Q47" s="21">
         <v>1</v>
@@ -5110,7 +5110,7 @@
         <v>2</v>
       </c>
       <c r="T47" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U47" s="21">
         <v>1</v>
@@ -5122,13 +5122,13 @@
         <v>1</v>
       </c>
       <c r="X47" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y47" s="21">
         <v>0</v>
       </c>
       <c r="Z47" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA47" s="21">
         <v>0</v>
@@ -5136,52 +5136,52 @@
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E48" s="12">
         <v>1</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G48" s="13">
         <v>2</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I48" s="12">
         <v>1</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K48" s="13">
         <v>2</v>
       </c>
       <c r="L48" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="M48" s="12">
         <v>1</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O48" s="12">
         <v>3</v>
       </c>
       <c r="P48" s="11" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="Q48" s="12">
         <v>1</v>
@@ -5193,25 +5193,25 @@
         <v>2</v>
       </c>
       <c r="T48" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U48" s="12">
         <v>1</v>
       </c>
       <c r="V48" s="11" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="W48" s="12">
         <v>1</v>
       </c>
       <c r="X48" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y48" s="12">
         <v>0</v>
       </c>
       <c r="Z48" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA48" s="12">
         <v>0</v>
@@ -5219,52 +5219,52 @@
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E49" s="21">
         <v>2</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G49" s="22">
         <v>2</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I49" s="21" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="J49" s="20" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K49" s="22">
         <v>2</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M49" s="21">
         <v>1</v>
       </c>
       <c r="N49" s="20" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O49" s="21">
         <v>3</v>
       </c>
       <c r="P49" s="20" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Q49" s="21">
         <v>1</v>
@@ -5276,25 +5276,25 @@
         <v>1</v>
       </c>
       <c r="T49" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U49" s="21">
         <v>1</v>
       </c>
       <c r="V49" s="20" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="W49" s="21">
         <v>2</v>
       </c>
       <c r="X49" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y49" s="21">
         <v>0</v>
       </c>
       <c r="Z49" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA49" s="21">
         <v>0</v>
@@ -5302,52 +5302,52 @@
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E50" s="12">
         <v>1</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G50" s="13">
         <v>3</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I50" s="12">
         <v>1</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K50" s="13">
         <v>3</v>
       </c>
       <c r="L50" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M50" s="12">
         <v>1</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O50" s="12">
         <v>3</v>
       </c>
       <c r="P50" s="11" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="Q50" s="12">
         <v>1</v>
@@ -5359,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="T50" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U50" s="12">
         <v>1</v>
@@ -5371,13 +5371,13 @@
         <v>1</v>
       </c>
       <c r="X50" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y50" s="12">
         <v>0</v>
       </c>
       <c r="Z50" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA50" s="12">
         <v>0</v>
@@ -5385,52 +5385,52 @@
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E51" s="21">
         <v>1</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G51" s="22">
         <v>3</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I51" s="21">
         <v>1</v>
       </c>
       <c r="J51" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K51" s="22">
         <v>3</v>
       </c>
       <c r="L51" s="23" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="M51" s="21">
         <v>1</v>
       </c>
       <c r="N51" s="20" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O51" s="21">
         <v>3</v>
       </c>
       <c r="P51" s="20" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="Q51" s="21">
         <v>1</v>
@@ -5442,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="T51" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U51" s="21">
         <v>1</v>
@@ -5454,13 +5454,13 @@
         <v>1</v>
       </c>
       <c r="X51" s="20" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="Y51" s="21">
         <v>1</v>
       </c>
       <c r="Z51" s="43" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA51" s="21">
         <v>0</v>
@@ -5468,52 +5468,52 @@
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E52" s="12">
         <v>1</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G52" s="13">
         <v>2</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I52" s="12">
         <v>1</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K52" s="13">
         <v>2</v>
       </c>
       <c r="L52" s="14" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="M52" s="12">
         <v>1</v>
       </c>
       <c r="N52" s="11" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O52" s="12">
         <v>3</v>
       </c>
       <c r="P52" s="11" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="Q52" s="12">
         <v>1</v>
@@ -5525,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="T52" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U52" s="12">
         <v>1</v>
@@ -5537,13 +5537,13 @@
         <v>1</v>
       </c>
       <c r="X52" s="11" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="Y52" s="12">
         <v>1</v>
       </c>
       <c r="Z52" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA52" s="12">
         <v>0</v>
@@ -5551,52 +5551,52 @@
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E53" s="21">
         <v>2</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G53" s="22">
         <v>2</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I53" s="21">
         <v>2</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K53" s="22">
         <v>2</v>
       </c>
       <c r="L53" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M53" s="21">
         <v>1</v>
       </c>
       <c r="N53" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O53" s="21">
         <v>3</v>
       </c>
       <c r="P53" s="20" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="Q53" s="21">
         <v>1</v>
@@ -5608,7 +5608,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U53" s="21">
         <v>1</v>
@@ -5620,13 +5620,13 @@
         <v>1</v>
       </c>
       <c r="X53" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y53" s="21">
         <v>0</v>
       </c>
       <c r="Z53" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA53" s="21">
         <v>0</v>
@@ -5634,52 +5634,52 @@
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E54" s="12">
         <v>1</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G54" s="13">
         <v>1</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I54" s="12">
         <v>1</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="K54" s="13">
         <v>1</v>
       </c>
       <c r="L54" s="14" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M54" s="12">
         <v>1</v>
       </c>
       <c r="N54" s="11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O54" s="12">
         <v>2</v>
       </c>
       <c r="P54" s="11" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="Q54" s="12">
         <v>1</v>
@@ -5691,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U54" s="12">
         <v>1</v>
@@ -5703,13 +5703,13 @@
         <v>1</v>
       </c>
       <c r="X54" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y54" s="12">
         <v>0</v>
       </c>
       <c r="Z54" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA54" s="12">
         <v>0</v>
@@ -5717,52 +5717,52 @@
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" s="17" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E55" s="21">
         <v>1</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G55" s="22">
         <v>3</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="I55" s="21">
         <v>1</v>
       </c>
       <c r="J55" s="20" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="K55" s="22">
         <v>3</v>
       </c>
       <c r="L55" s="23" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M55" s="21">
         <v>1</v>
       </c>
       <c r="N55" s="20" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="O55" s="21">
         <v>2</v>
       </c>
       <c r="P55" s="20" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="Q55" s="21">
         <v>1</v>
@@ -5774,7 +5774,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="20" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U55" s="21">
         <v>1</v>
@@ -5786,13 +5786,13 @@
         <v>1</v>
       </c>
       <c r="X55" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y55" s="21">
         <v>0</v>
       </c>
       <c r="Z55" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA55" s="21">
         <v>0</v>
@@ -5800,52 +5800,52 @@
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E56" s="12">
         <v>1</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G56" s="13">
         <v>3</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I56" s="12">
         <v>1</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="K56" s="13">
         <v>3</v>
       </c>
       <c r="L56" s="14" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M56" s="12">
         <v>1</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O56" s="12">
         <v>1</v>
       </c>
       <c r="P56" s="11" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q56" s="12">
         <v>1</v>
@@ -5857,7 +5857,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U56" s="12">
         <v>1</v>
@@ -5869,13 +5869,13 @@
         <v>1</v>
       </c>
       <c r="X56" s="11" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="Y56" s="12">
         <v>1</v>
       </c>
       <c r="Z56" s="11" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA56" s="12">
         <v>0</v>
@@ -5883,52 +5883,52 @@
     </row>
     <row r="57" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="49" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B57" s="50" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D57" s="52" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E57" s="53">
         <v>4</v>
       </c>
       <c r="F57" s="52" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G57" s="54">
         <v>0</v>
       </c>
       <c r="H57" s="55" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I57" s="53">
         <v>1</v>
       </c>
       <c r="J57" s="52" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K57" s="54">
         <v>3</v>
       </c>
       <c r="L57" s="55" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="M57" s="53">
         <v>1</v>
       </c>
       <c r="N57" s="52" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O57" s="53">
         <v>3</v>
       </c>
       <c r="P57" s="52" t="s">
-        <v>146</v>
+        <v>62</v>
       </c>
       <c r="Q57" s="53">
         <v>1</v>
@@ -5940,7 +5940,7 @@
         <v>2</v>
       </c>
       <c r="T57" s="52" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U57" s="53">
         <v>1</v>
@@ -5952,13 +5952,13 @@
         <v>1</v>
       </c>
       <c r="X57" s="52" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="Y57" s="53">
         <v>0</v>
       </c>
       <c r="Z57" s="52" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AA57" s="53">
         <v>0</v>
@@ -5969,11 +5969,11 @@
     </row>
     <row r="59" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="59" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="B59" s="60"/>
       <c r="C59" s="59" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.3">

--- a/cadet_data/CadetData_OCP.xlsx
+++ b/cadet_data/CadetData_OCP.xlsx
@@ -574,8 +574,10 @@
           <t>M/R</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -590,8 +592,10 @@
           <t>L/R</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -606,44 +610,60 @@
           <t>M/R</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>1</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>10.5R</t>
         </is>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>S/M</t>
         </is>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>44</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1119,92 +1139,100 @@
           <t>S/S</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>S/S</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>1</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>S/S</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>1</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>1</v>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>9.5R</t>
         </is>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7.125</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>7.125</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>S/M</t>
         </is>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>34</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
